--- a/NY_State_Reports_2026-10-16/Caesars_Sport_Book_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-16/Caesars_Sport_Book_Weekly_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756C7F3B-4DFF-42A5-9D65-8AFD51D7415D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEF2609-1CB7-4BCE-AF37-C4BC4410475E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
   <sheets>
     <sheet name="FY 26-27" sheetId="7" r:id="rId1"/>
@@ -2858,7 +2858,12 @@
         <v>46306</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="F41" s="32"/>
+      <c r="C41" s="20">
+        <v>39377883.089999996</v>
+      </c>
+      <c r="F41" s="32">
+        <v>3511389.5300000003</v>
+      </c>
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
@@ -3399,11 +3404,11 @@
       </c>
       <c r="C67" s="22">
         <f>SUM(C13:C66)</f>
-        <v>885588120.43000007</v>
+        <v>924966003.5200001</v>
       </c>
       <c r="F67" s="22">
         <f>SUM(F13:F66)</f>
-        <v>63710474.520000011</v>
+        <v>67221864.050000012</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
